--- a/salidas/empresas/INTU.xlsx
+++ b/salidas/empresas/INTU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.87909317016602</v>
+        <v>22.87910079956055</v>
       </c>
       <c r="C2" t="n">
         <v>26.16500091552734</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>21.25268363952637</v>
+        <v>21.2526741027832</v>
       </c>
       <c r="C3" t="n">
         <v>24.30500030517578</v>
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.68355560302734</v>
+        <v>23.68354606628418</v>
       </c>
       <c r="C5" t="n">
         <v>27.08499908447266</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>24.17323112487793</v>
+        <v>24.17323684692383</v>
       </c>
       <c r="C6" t="n">
         <v>27.64500045776367</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>26.46856880187988</v>
+        <v>26.46857261657715</v>
       </c>
       <c r="C7" t="n">
         <v>30.27000045776367</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>26.99322128295898</v>
+        <v>26.99322319030762</v>
       </c>
       <c r="C8" t="n">
         <v>30.8700008392334</v>
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.06001091003418</v>
+        <v>28.06001281738281</v>
       </c>
       <c r="C10" t="n">
         <v>32.09000015258789</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.86687469482422</v>
+        <v>30.86686134338379</v>
       </c>
       <c r="C11" t="n">
         <v>35.29999923706055</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>26.67843246459961</v>
+        <v>26.67842483520508</v>
       </c>
       <c r="C13" t="n">
         <v>30.51000022888184</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.50038146972656</v>
+        <v>27.50039100646973</v>
       </c>
       <c r="C14" t="n">
         <v>31.45000076293945</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.80401992797852</v>
+        <v>25.80401611328125</v>
       </c>
       <c r="C15" t="n">
         <v>29.51000022888184</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.92401885986328</v>
+        <v>23.92401695251465</v>
       </c>
       <c r="C16" t="n">
         <v>27.36000061035156</v>
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>26.30244064331055</v>
+        <v>26.30243301391602</v>
       </c>
       <c r="C19" t="n">
         <v>30.07999992370605</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>25.04327201843262</v>
+        <v>25.04327011108398</v>
       </c>
       <c r="C20" t="n">
         <v>28.63999938964844</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>23.88030052185059</v>
+        <v>23.88029861450195</v>
       </c>
       <c r="C21" t="n">
         <v>27.30999946594238</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>26.49480056762695</v>
+        <v>26.49480438232422</v>
       </c>
       <c r="C22" t="n">
         <v>30.29999923706055</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.12995529174805</v>
+        <v>28.12995910644531</v>
       </c>
       <c r="C23" t="n">
         <v>32.16999816894531</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>27.64028358459473</v>
+        <v>27.64029312133789</v>
       </c>
       <c r="C25" t="n">
         <v>31.61000061035156</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>26.83582305908203</v>
+        <v>26.83582496643066</v>
       </c>
       <c r="C26" t="n">
         <v>30.69000053405762</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>23.22448348999023</v>
+        <v>23.22449111938477</v>
       </c>
       <c r="C27" t="n">
         <v>26.55999946594238</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>23.61797523498535</v>
+        <v>23.61797142028809</v>
       </c>
       <c r="C28" t="n">
         <v>27.01000022888184</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>23.58298873901367</v>
+        <v>23.5829906463623</v>
       </c>
       <c r="C29" t="n">
         <v>26.96999931335449</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>25.32308387756348</v>
+        <v>25.32309150695801</v>
       </c>
       <c r="C30" t="n">
         <v>28.95999908447266</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.10765075683594</v>
+        <v>24.10764694213867</v>
       </c>
       <c r="C31" t="n">
         <v>27.56999969482422</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.89779090881348</v>
+        <v>23.89778518676758</v>
       </c>
       <c r="C32" t="n">
         <v>27.32999992370605</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.2936840057373</v>
+        <v>26.29368019104004</v>
       </c>
       <c r="C33" t="n">
         <v>30.06999969482422</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>27.64028358459473</v>
+        <v>27.64029312133789</v>
       </c>
       <c r="C34" t="n">
         <v>31.61000061035156</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.91286087036133</v>
+        <v>21.91285514831543</v>
       </c>
       <c r="C35" t="n">
         <v>25.05999946594238</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.80235481262207</v>
+        <v>20.8023567199707</v>
       </c>
       <c r="C37" t="n">
         <v>23.79000091552734</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.80551910400391</v>
+        <v>19.8055248260498</v>
       </c>
       <c r="C38" t="n">
         <v>22.64999961853027</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>19.92793846130371</v>
+        <v>19.92794036865234</v>
       </c>
       <c r="C39" t="n">
         <v>22.79000091552734</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>23.60922622680664</v>
+        <v>23.60922813415527</v>
       </c>
       <c r="C40" t="n">
         <v>27</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.2252311706543</v>
+        <v>20.22524261474609</v>
       </c>
       <c r="C41" t="n">
         <v>23.1299991607666</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>23.80160522460938</v>
+        <v>23.80159950256348</v>
       </c>
       <c r="C42" t="n">
         <v>27.21999931335449</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.6497917175293</v>
+        <v>24.64978408813477</v>
       </c>
       <c r="C43" t="n">
         <v>28.19000053405762</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.97014808654785</v>
+        <v>25.97015953063965</v>
       </c>
       <c r="C44" t="n">
         <v>29.70000076293945</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.28252410888672</v>
+        <v>24.28253173828125</v>
       </c>
       <c r="C45" t="n">
         <v>27.77000045776367</v>
@@ -1318,11 +1330,11 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>24.92085075378418</v>
+        <v>24.92085838317871</v>
       </c>
       <c r="C46" t="n">
         <v>28.5</v>
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>25.41926193237305</v>
+        <v>25.41927146911621</v>
       </c>
       <c r="C47" t="n">
         <v>29.06999969482422</v>
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>26.87079620361328</v>
+        <v>26.87080192565918</v>
       </c>
       <c r="C49" t="n">
         <v>30.72999954223633</v>
@@ -1400,11 +1412,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.89146041870117</v>
+        <v>25.89145851135254</v>
       </c>
       <c r="C50" t="n">
         <v>29.61000061035156</v>
@@ -1425,11 +1437,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>28.29609870910645</v>
+        <v>28.29610061645508</v>
       </c>
       <c r="C51" t="n">
         <v>32.36000061035156</v>
@@ -1450,7 +1462,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1475,11 +1487,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.64511299133301</v>
+        <v>31.64511108398438</v>
       </c>
       <c r="C53" t="n">
         <v>36.18999862670898</v>
@@ -1500,11 +1512,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>31.25163269042969</v>
+        <v>31.25163841247559</v>
       </c>
       <c r="C54" t="n">
         <v>35.7400016784668</v>
@@ -1525,11 +1537,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>30.40343856811523</v>
+        <v>30.40345191955566</v>
       </c>
       <c r="C55" t="n">
         <v>34.77000045776367</v>
@@ -1550,11 +1562,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>34.75803375244141</v>
+        <v>34.75802612304688</v>
       </c>
       <c r="C56" t="n">
         <v>39.75</v>
@@ -1575,11 +1587,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>37.37254333496094</v>
+        <v>37.37253952026367</v>
       </c>
       <c r="C57" t="n">
         <v>42.7400016784668</v>
@@ -1600,7 +1612,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1629,11 +1641,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>41.9544792175293</v>
+        <v>41.95447158813477</v>
       </c>
       <c r="C59" t="n">
         <v>47.97999954223633</v>
@@ -1658,7 +1670,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1687,7 +1699,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1716,11 +1728,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>41.03634643554688</v>
+        <v>41.03632736206055</v>
       </c>
       <c r="C62" t="n">
         <v>46.93000030517578</v>
@@ -1745,11 +1757,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>45.97679901123047</v>
+        <v>45.97678756713867</v>
       </c>
       <c r="C63" t="n">
         <v>52.58000183105469</v>
@@ -1774,7 +1786,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1803,11 +1815,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>48.58254241943359</v>
+        <v>48.58254623413086</v>
       </c>
       <c r="C65" t="n">
         <v>55.56000137329102</v>
@@ -1828,11 +1840,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>47.19223785400391</v>
+        <v>47.19221878051758</v>
       </c>
       <c r="C66" t="n">
         <v>53.97000122070312</v>
@@ -1853,11 +1865,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>45.34720993041992</v>
+        <v>45.34721374511719</v>
       </c>
       <c r="C67" t="n">
         <v>51.86000061035156</v>
@@ -1878,11 +1890,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.83523941040039</v>
+        <v>40.83523178100586</v>
       </c>
       <c r="C68" t="n">
         <v>46.70000076293945</v>
@@ -1903,11 +1915,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>43.13494110107422</v>
+        <v>43.13494873046875</v>
       </c>
       <c r="C69" t="n">
         <v>49.33000183105469</v>
@@ -1928,7 +1940,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1957,11 +1969,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>47.08046722412109</v>
+        <v>47.08047485351562</v>
       </c>
       <c r="C71" t="n">
         <v>53.66999816894531</v>
@@ -1986,11 +1998,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>46.70327758789062</v>
+        <v>46.70327377319336</v>
       </c>
       <c r="C72" t="n">
         <v>53.2400016784668</v>
@@ -2015,11 +2027,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>46.13308334350586</v>
+        <v>46.13307571411133</v>
       </c>
       <c r="C73" t="n">
         <v>52.59000015258789</v>
@@ -2044,11 +2056,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>49.65213012695312</v>
+        <v>49.65213394165039</v>
       </c>
       <c r="C74" t="n">
         <v>56.43999862670898</v>
@@ -2073,11 +2085,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>50.88377380371094</v>
+        <v>50.88376998901367</v>
       </c>
       <c r="C75" t="n">
         <v>57.84000015258789</v>
@@ -2102,11 +2114,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>52.92475509643555</v>
+        <v>52.92474746704102</v>
       </c>
       <c r="C76" t="n">
         <v>60.15999984741211</v>
@@ -2131,11 +2143,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>51.12728881835938</v>
+        <v>51.12728118896484</v>
       </c>
       <c r="C77" t="n">
         <v>57.97000122070312</v>
@@ -2160,11 +2172,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>49.59268569946289</v>
+        <v>49.59268188476562</v>
       </c>
       <c r="C78" t="n">
         <v>56.22999954223633</v>
@@ -2189,11 +2201,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>52.34438323974609</v>
+        <v>52.34439086914062</v>
       </c>
       <c r="C79" t="n">
         <v>59.34999847412109</v>
@@ -2218,11 +2230,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>51.29979705810547</v>
+        <v>51.29982757568359</v>
       </c>
       <c r="C80" t="n">
         <v>58.02000045776367</v>
@@ -2247,11 +2259,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>51.75956344604492</v>
+        <v>51.75957489013672</v>
       </c>
       <c r="C81" t="n">
         <v>58.54000091552734</v>
@@ -2276,11 +2288,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>52.0601921081543</v>
+        <v>52.06018829345703</v>
       </c>
       <c r="C82" t="n">
         <v>58.88000106811523</v>
@@ -2305,11 +2317,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.69318771362305</v>
+        <v>52.69316101074219</v>
       </c>
       <c r="C83" t="n">
         <v>59.43000030517578</v>
@@ -2334,7 +2346,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2363,11 +2375,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>52.73751068115234</v>
+        <v>52.73749542236328</v>
       </c>
       <c r="C85" t="n">
         <v>59.47999954223633</v>
@@ -2392,11 +2404,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>55.46010971069336</v>
+        <v>55.46012496948242</v>
       </c>
       <c r="C86" t="n">
         <v>62.38000106811523</v>
@@ -2421,11 +2433,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.31829452514648</v>
+        <v>57.31827545166016</v>
       </c>
       <c r="C87" t="n">
         <v>64.47000122070312</v>
@@ -2450,11 +2462,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.37626647949219</v>
+        <v>58.37627410888672</v>
       </c>
       <c r="C88" t="n">
         <v>65.66000366210938</v>
@@ -2479,7 +2491,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2508,11 +2520,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>52.09457778930664</v>
+        <v>52.09458923339844</v>
       </c>
       <c r="C90" t="n">
         <v>58.43999862670898</v>
@@ -2537,11 +2549,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>54.41228103637695</v>
+        <v>54.41226959228516</v>
       </c>
       <c r="C91" t="n">
         <v>61.04000091552734</v>
@@ -2566,11 +2578,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.13483810424805</v>
+        <v>57.13484573364258</v>
       </c>
       <c r="C92" t="n">
         <v>63.91999816894531</v>
@@ -2595,7 +2607,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2624,11 +2636,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>59.27114486694336</v>
+        <v>59.27115249633789</v>
       </c>
       <c r="C94" t="n">
         <v>66.30999755859375</v>
@@ -2653,11 +2665,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>64.01338958740234</v>
+        <v>64.013427734375</v>
       </c>
       <c r="C95" t="n">
         <v>71.41000366210938</v>
@@ -2682,11 +2694,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>66.54129791259766</v>
+        <v>66.54128265380859</v>
       </c>
       <c r="C96" t="n">
         <v>74.23000335693359</v>
@@ -2711,11 +2723,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>68.41483306884766</v>
+        <v>68.41482543945312</v>
       </c>
       <c r="C97" t="n">
         <v>76.31999969482422</v>
@@ -2740,11 +2752,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>65.82513427734375</v>
+        <v>65.82508850097656</v>
       </c>
       <c r="C98" t="n">
         <v>73.25</v>
@@ -2769,11 +2781,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>70.22843170166016</v>
+        <v>70.22842407226562</v>
       </c>
       <c r="C99" t="n">
         <v>78.15000152587891</v>
@@ -2798,7 +2810,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2827,11 +2839,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>68.24505615234375</v>
+        <v>68.24507904052734</v>
       </c>
       <c r="C101" t="n">
         <v>75.75</v>
@@ -2856,11 +2868,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>71.43434143066406</v>
+        <v>71.43431854248047</v>
       </c>
       <c r="C102" t="n">
         <v>79.29000091552734</v>
@@ -2885,7 +2897,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2914,11 +2926,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.02199554443359</v>
+        <v>74.02197265625</v>
       </c>
       <c r="C104" t="n">
         <v>81.97000122070312</v>
@@ -2943,11 +2955,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>75.11464691162109</v>
+        <v>75.11465454101562</v>
       </c>
       <c r="C105" t="n">
         <v>83.18000030517578</v>
@@ -2972,11 +2984,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>79.1512451171875</v>
+        <v>79.15123748779297</v>
       </c>
       <c r="C106" t="n">
         <v>87.65000152587891</v>
@@ -3001,11 +3013,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>79.718017578125</v>
+        <v>79.71800231933594</v>
       </c>
       <c r="C107" t="n">
         <v>88.01000213623047</v>
@@ -3030,7 +3042,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3059,11 +3071,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>83.50418090820312</v>
+        <v>83.504150390625</v>
       </c>
       <c r="C109" t="n">
         <v>92.19000244140625</v>
@@ -3088,11 +3100,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>78.86398315429688</v>
+        <v>78.86399841308594</v>
       </c>
       <c r="C110" t="n">
         <v>86.81999969482422</v>
@@ -3117,11 +3129,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>88.68338012695312</v>
+        <v>88.68337249755859</v>
       </c>
       <c r="C111" t="n">
         <v>97.62999725341797</v>
@@ -3146,11 +3158,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>88.07479095458984</v>
+        <v>88.07478332519531</v>
       </c>
       <c r="C112" t="n">
         <v>96.95999908447266</v>
@@ -3175,7 +3187,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3204,7 +3216,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3233,7 +3245,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3262,11 +3274,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>96.557861328125</v>
+        <v>96.55787658691406</v>
       </c>
       <c r="C116" t="n">
         <v>105.7699966430664</v>
@@ -3291,11 +3303,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>78.28153228759766</v>
+        <v>78.28153991699219</v>
       </c>
       <c r="C117" t="n">
         <v>85.75</v>
@@ -3320,7 +3332,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3349,7 +3361,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3378,11 +3390,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>91.77617645263672</v>
+        <v>91.77618408203125</v>
       </c>
       <c r="C120" t="n">
         <v>100.1999969482422</v>
@@ -3407,11 +3419,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>88.38722991943359</v>
+        <v>88.38726806640625</v>
       </c>
       <c r="C121" t="n">
         <v>96.5</v>
@@ -3436,11 +3448,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>87.75389099121094</v>
+        <v>87.75390625</v>
       </c>
       <c r="C122" t="n">
         <v>95.51000213623047</v>
@@ -3465,7 +3477,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3494,11 +3506,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>95.56364440917969</v>
+        <v>95.56362152099609</v>
       </c>
       <c r="C124" t="n">
         <v>104.0100021362305</v>
@@ -3523,7 +3535,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3552,11 +3564,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>98.27886199951172</v>
+        <v>98.27886962890625</v>
       </c>
       <c r="C126" t="n">
         <v>106.6600036621094</v>
@@ -3581,11 +3593,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>102.8399276733398</v>
+        <v>102.8399353027344</v>
       </c>
       <c r="C127" t="n">
         <v>111.6100006103516</v>
@@ -3610,11 +3622,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>102.5378952026367</v>
+        <v>102.5379028320312</v>
       </c>
       <c r="C128" t="n">
         <v>110.9899978637695</v>
@@ -3639,11 +3651,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>102.9628524780273</v>
+        <v>102.9628448486328</v>
       </c>
       <c r="C129" t="n">
         <v>111.4499969482422</v>
@@ -3668,11 +3680,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>101.6324996948242</v>
+        <v>101.6325225830078</v>
       </c>
       <c r="C130" t="n">
         <v>110.0100021362305</v>
@@ -3697,11 +3709,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>100.7725067138672</v>
+        <v>100.7724761962891</v>
       </c>
       <c r="C131" t="n">
         <v>108.7399978637695</v>
@@ -3726,11 +3738,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>105.3505172729492</v>
+        <v>105.3505401611328</v>
       </c>
       <c r="C132" t="n">
         <v>113.6800003051758</v>
@@ -3755,11 +3767,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>106.21240234375</v>
+        <v>106.2123947143555</v>
       </c>
       <c r="C133" t="n">
         <v>114.6100006103516</v>
@@ -3784,11 +3796,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>110.2154083251953</v>
+        <v>110.2154235839844</v>
       </c>
       <c r="C134" t="n">
         <v>118.5800018310547</v>
@@ -3813,11 +3825,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>116.5915145874023</v>
+        <v>116.5915069580078</v>
       </c>
       <c r="C135" t="n">
         <v>125.4400024414062</v>
@@ -3842,11 +3854,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>107.8081207275391</v>
+        <v>107.80810546875</v>
       </c>
       <c r="C136" t="n">
         <v>115.9899978637695</v>
@@ -3871,7 +3883,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3900,11 +3912,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>131.101806640625</v>
+        <v>131.1017608642578</v>
       </c>
       <c r="C138" t="n">
         <v>140.6399993896484</v>
@@ -3929,11 +3941,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>123.8028030395508</v>
+        <v>123.8027572631836</v>
       </c>
       <c r="C139" t="n">
         <v>132.8099975585938</v>
@@ -3958,11 +3970,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>128.2347106933594</v>
+        <v>128.2347259521484</v>
       </c>
       <c r="C140" t="n">
         <v>137.2100067138672</v>
@@ -3987,11 +3999,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>132.1973724365234</v>
+        <v>132.1973571777344</v>
       </c>
       <c r="C141" t="n">
         <v>141.4499969482422</v>
@@ -4016,11 +4028,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>132.8422698974609</v>
+        <v>132.8422546386719</v>
       </c>
       <c r="C142" t="n">
         <v>142.1399993896484</v>
@@ -4045,11 +4057,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>141.5277557373047</v>
+        <v>141.5277404785156</v>
       </c>
       <c r="C143" t="n">
         <v>151.0200042724609</v>
@@ -4074,7 +4086,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4103,11 +4115,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>147.8628387451172</v>
+        <v>147.8628692626953</v>
       </c>
       <c r="C145" t="n">
         <v>157.7799987792969</v>
@@ -4132,11 +4144,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>157.7213439941406</v>
+        <v>157.7213592529297</v>
       </c>
       <c r="C146" t="n">
         <v>167.8999938964844</v>
@@ -4161,11 +4173,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>156.7444610595703</v>
+        <v>156.7444152832031</v>
       </c>
       <c r="C147" t="n">
         <v>166.8600006103516</v>
@@ -4190,11 +4202,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>162.8409881591797</v>
+        <v>162.8409729003906</v>
       </c>
       <c r="C148" t="n">
         <v>173.3500061035156</v>
@@ -4219,11 +4231,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>173.9921417236328</v>
+        <v>173.9920654296875</v>
       </c>
       <c r="C149" t="n">
         <v>184.7899932861328</v>
@@ -4248,11 +4260,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>189.8198394775391</v>
+        <v>189.81982421875</v>
       </c>
       <c r="C150" t="n">
         <v>201.6000061035156</v>
@@ -4277,11 +4289,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>192.3714752197266</v>
+        <v>192.3714904785156</v>
       </c>
       <c r="C151" t="n">
         <v>204.3099975585938</v>
@@ -4306,11 +4318,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>192.6665954589844</v>
+        <v>192.6666107177734</v>
       </c>
       <c r="C152" t="n">
         <v>204.2400054931641</v>
@@ -4335,11 +4347,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>207.0335845947266</v>
+        <v>207.0335540771484</v>
       </c>
       <c r="C153" t="n">
         <v>219.4700012207031</v>
@@ -4364,11 +4376,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>214.5141906738281</v>
+        <v>214.5142364501953</v>
       </c>
       <c r="C154" t="n">
         <v>227.3999938964844</v>
@@ -4393,11 +4405,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>199.4748992919922</v>
+        <v>199.4749145507812</v>
       </c>
       <c r="C155" t="n">
         <v>211</v>
@@ -4422,11 +4434,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>202.8120880126953</v>
+        <v>202.8121185302734</v>
       </c>
       <c r="C156" t="n">
         <v>214.5299987792969</v>
@@ -4451,11 +4463,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>186.0978240966797</v>
+        <v>186.0977935791016</v>
       </c>
       <c r="C157" t="n">
         <v>196.8500061035156</v>
@@ -4480,11 +4492,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>204.5033416748047</v>
+        <v>204.5033721923828</v>
       </c>
       <c r="C158" t="n">
         <v>215.8200073242188</v>
@@ -4509,11 +4521,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>234.1715850830078</v>
+        <v>234.1715698242188</v>
       </c>
       <c r="C159" t="n">
         <v>247.1300048828125</v>
@@ -4538,11 +4550,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>247.7027893066406</v>
+        <v>247.7028350830078</v>
       </c>
       <c r="C160" t="n">
         <v>261.4100036621094</v>
@@ -4567,7 +4579,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4596,11 +4608,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>232.4300842285156</v>
+        <v>232.4300689697266</v>
       </c>
       <c r="C162" t="n">
         <v>244.8500061035156</v>
@@ -4625,7 +4637,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4654,11 +4666,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>263.7006530761719</v>
+        <v>263.7006225585938</v>
       </c>
       <c r="C164" t="n">
         <v>277.3099975585938</v>
@@ -4683,11 +4695,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>274.2083435058594</v>
+        <v>274.2084045410156</v>
       </c>
       <c r="C165" t="n">
         <v>288.3599853515625</v>
@@ -4712,11 +4724,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>252.8886566162109</v>
+        <v>252.8886871337891</v>
       </c>
       <c r="C166" t="n">
         <v>265.9400024414062</v>
@@ -4741,7 +4753,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4770,11 +4782,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>246.6855926513672</v>
+        <v>246.6856079101562</v>
       </c>
       <c r="C168" t="n">
         <v>258.8900146484375</v>
@@ -4799,11 +4811,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>249.5822906494141</v>
+        <v>249.5822601318359</v>
       </c>
       <c r="C169" t="n">
         <v>261.9299926757812</v>
@@ -4828,11 +4840,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>267.6824035644531</v>
+        <v>267.6824340820312</v>
       </c>
       <c r="C170" t="n">
         <v>280.3800048828125</v>
@@ -4857,11 +4869,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>253.8104248046875</v>
+        <v>253.8105010986328</v>
       </c>
       <c r="C171" t="n">
         <v>265.8500061035156</v>
@@ -4886,7 +4898,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4915,11 +4927,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>258.1474304199219</v>
+        <v>258.1473999023438</v>
       </c>
       <c r="C173" t="n">
         <v>269.8099975585938</v>
@@ -4944,11 +4956,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>277.7709350585938</v>
+        <v>277.7708435058594</v>
       </c>
       <c r="C174" t="n">
         <v>290.3200073242188</v>
@@ -4973,7 +4985,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5002,11 +5014,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>293.6285095214844</v>
+        <v>293.6285400390625</v>
       </c>
       <c r="C176" t="n">
         <v>306.3699951171875</v>
@@ -5031,11 +5043,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>331.0257873535156</v>
+        <v>331.0257568359375</v>
       </c>
       <c r="C177" t="n">
         <v>345.3900146484375</v>
@@ -5060,11 +5072,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>312.6433715820312</v>
+        <v>312.6434020996094</v>
       </c>
       <c r="C178" t="n">
         <v>326.2099914550781</v>
@@ -5089,11 +5101,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>302.1251831054688</v>
+        <v>302.125244140625</v>
       </c>
       <c r="C179" t="n">
         <v>314.6799926757812</v>
@@ -5118,11 +5130,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>337.9753723144531</v>
+        <v>337.9754028320312</v>
       </c>
       <c r="C180" t="n">
         <v>352.0199890136719</v>
@@ -5147,11 +5159,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>364.6951293945312</v>
+        <v>364.6951599121094</v>
       </c>
       <c r="C181" t="n">
         <v>379.8500061035156</v>
@@ -5176,11 +5188,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>347.3739929199219</v>
+        <v>347.3739624023438</v>
       </c>
       <c r="C182" t="n">
         <v>361.2300109863281</v>
@@ -5205,7 +5217,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5234,11 +5246,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>368.3666381835938</v>
+        <v>368.3665161132812</v>
       </c>
       <c r="C184" t="n">
         <v>383.0599975585938</v>
@@ -5263,11 +5275,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>396.9197692871094</v>
+        <v>396.9197082519531</v>
       </c>
       <c r="C185" t="n">
         <v>412.1600036621094</v>
@@ -5292,11 +5304,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>422.8539123535156</v>
+        <v>422.8539733886719</v>
       </c>
       <c r="C186" t="n">
         <v>439.0899963378906</v>
@@ -5321,11 +5333,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>472.045166015625</v>
+        <v>472.0451965332031</v>
       </c>
       <c r="C187" t="n">
         <v>490.1700134277344</v>
@@ -5350,11 +5362,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>510.9690856933594</v>
+        <v>510.9690551757812</v>
       </c>
       <c r="C188" t="n">
         <v>529.969970703125</v>
@@ -5379,7 +5391,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5408,7 +5420,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5437,11 +5449,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>604.3153076171875</v>
+        <v>604.3152465820312</v>
       </c>
       <c r="C191" t="n">
         <v>625.989990234375</v>
@@ -5466,11 +5478,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>629.7142333984375</v>
+        <v>629.7142944335938</v>
       </c>
       <c r="C192" t="n">
         <v>652.2999877929688</v>
@@ -5495,7 +5507,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5524,11 +5536,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>536.6275634765625</v>
+        <v>536.627685546875</v>
       </c>
       <c r="C194" t="n">
         <v>555.22998046875</v>
@@ -5553,11 +5565,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>458.4767456054688</v>
+        <v>458.4767761230469</v>
       </c>
       <c r="C195" t="n">
         <v>474.3699951171875</v>
@@ -5582,11 +5594,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>464.72998046875</v>
+        <v>464.7300109863281</v>
       </c>
       <c r="C196" t="n">
         <v>480.8399963378906</v>
@@ -5611,11 +5623,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>405.2769470214844</v>
+        <v>405.2769775390625</v>
       </c>
       <c r="C197" t="n">
         <v>418.75</v>
@@ -5640,11 +5652,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>401.1250305175781</v>
+        <v>401.1249694824219</v>
       </c>
       <c r="C198" t="n">
         <v>414.4599914550781</v>
@@ -5669,11 +5681,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>373.0386962890625</v>
+        <v>373.0386657714844</v>
       </c>
       <c r="C199" t="n">
         <v>385.4400024414062</v>
@@ -5698,11 +5710,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>442.2249450683594</v>
+        <v>442.2250366210938</v>
       </c>
       <c r="C200" t="n">
         <v>456.1700134277344</v>
@@ -5727,11 +5739,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>418.58056640625</v>
+        <v>418.5805969238281</v>
       </c>
       <c r="C201" t="n">
         <v>431.7799987792969</v>
@@ -5756,11 +5768,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>375.4796752929688</v>
+        <v>375.479736328125</v>
       </c>
       <c r="C202" t="n">
         <v>387.3200073242188</v>
@@ -5785,11 +5797,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>415.2144470214844</v>
+        <v>415.2145080566406</v>
       </c>
       <c r="C203" t="n">
         <v>427.5</v>
@@ -5814,11 +5826,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>395.8766479492188</v>
+        <v>395.8766784667969</v>
       </c>
       <c r="C204" t="n">
         <v>407.5899963378906</v>
@@ -5843,11 +5855,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>378.0346069335938</v>
+        <v>378.0346374511719</v>
       </c>
       <c r="C205" t="n">
         <v>389.2200012207031</v>
@@ -5872,11 +5884,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>411.3533935546875</v>
+        <v>411.3534240722656</v>
       </c>
       <c r="C206" t="n">
         <v>422.6700134277344</v>
@@ -5901,11 +5913,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>396.2781677246094</v>
+        <v>396.2781066894531</v>
       </c>
       <c r="C207" t="n">
         <v>407.1799926757812</v>
@@ -5930,11 +5942,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>433.893310546875</v>
+        <v>433.8932800292969</v>
       </c>
       <c r="C208" t="n">
         <v>445.8299865722656</v>
@@ -5959,11 +5971,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>432.8324584960938</v>
+        <v>432.8324279785156</v>
       </c>
       <c r="C209" t="n">
         <v>443.9500122070312</v>
@@ -5988,11 +6000,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>408.6241760253906</v>
+        <v>408.624267578125</v>
       </c>
       <c r="C210" t="n">
         <v>419.1199951171875</v>
@@ -6017,11 +6029,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>446.7157897949219</v>
+        <v>446.7158508300781</v>
       </c>
       <c r="C211" t="n">
         <v>458.1900024414062</v>
@@ -6046,11 +6058,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>499.7491760253906</v>
+        <v>499.7491455078125</v>
       </c>
       <c r="C212" t="n">
         <v>511.7000122070312</v>
@@ -6075,11 +6087,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>529.1558837890625</v>
+        <v>529.1559448242188</v>
       </c>
       <c r="C213" t="n">
         <v>541.8099975585938</v>
@@ -6104,7 +6116,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6133,11 +6145,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>484.2325439453125</v>
+        <v>484.2325744628906</v>
       </c>
       <c r="C215" t="n">
         <v>494.9500122070312</v>
@@ -6162,11 +6174,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>559.0858764648438</v>
+        <v>559.0858154296875</v>
       </c>
       <c r="C216" t="n">
         <v>571.4600219726562</v>
@@ -6191,7 +6203,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6220,11 +6232,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>618.58984375</v>
+        <v>618.5897827148438</v>
       </c>
       <c r="C218" t="n">
         <v>631.3300170898438</v>
@@ -6249,11 +6261,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>649.5130615234375</v>
+        <v>649.512939453125</v>
       </c>
       <c r="C219" t="n">
         <v>662.8900146484375</v>
@@ -6278,11 +6290,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>636.8832397460938</v>
+        <v>636.883056640625</v>
       </c>
       <c r="C220" t="n">
         <v>650</v>
@@ -6307,7 +6319,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6336,11 +6348,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>565.596435546875</v>
+        <v>565.5964965820312</v>
       </c>
       <c r="C222" t="n">
         <v>576.4400024414062</v>
@@ -6365,11 +6377,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>644.8469848632812</v>
+        <v>644.8471069335938</v>
       </c>
       <c r="C223" t="n">
         <v>657.2100219726562</v>
@@ -6394,11 +6406,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>636.0525512695312</v>
+        <v>636.0526123046875</v>
       </c>
       <c r="C224" t="n">
         <v>647.3499755859375</v>
@@ -6423,11 +6435,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>619.2609252929688</v>
+        <v>619.2608032226562</v>
       </c>
       <c r="C225" t="n">
         <v>630.260009765625</v>
@@ -6452,11 +6464,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>610.1624755859375</v>
+        <v>610.162353515625</v>
       </c>
       <c r="C226" t="n">
         <v>621</v>
@@ -6481,7 +6493,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6510,7 +6522,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6539,11 +6551,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>618.5665283203125</v>
+        <v>618.5664672851562</v>
       </c>
       <c r="C229" t="n">
         <v>628.5</v>
@@ -6568,7 +6580,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6597,7 +6609,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6626,11 +6638,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>605.2913818359375</v>
+        <v>605.2913208007812</v>
       </c>
       <c r="C232" t="n">
         <v>613.989990234375</v>
@@ -6655,11 +6667,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>619.6607055664062</v>
+        <v>619.6607666015625</v>
       </c>
       <c r="C233" t="n">
         <v>627.469970703125</v>
@@ -6684,11 +6696,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>744.0925903320312</v>
+        <v>744.092529296875</v>
       </c>
       <c r="C234" t="n">
         <v>753.469970703125</v>
@@ -6713,7 +6725,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6742,7 +6754,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6771,11 +6783,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>659.590087890625</v>
+        <v>659.5901489257812</v>
       </c>
       <c r="C237" t="n">
         <v>667</v>
@@ -6800,11 +6812,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>675.3233032226562</v>
+        <v>675.3233642578125</v>
       </c>
       <c r="C238" t="n">
         <v>682.9099731445312</v>
@@ -6829,7 +6841,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6858,11 +6870,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>628.1818237304688</v>
+        <v>628.1817626953125</v>
       </c>
       <c r="C240" t="n">
         <v>634.0800170898438</v>
@@ -6887,11 +6899,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>656.2581787109375</v>
+        <v>656.2581176757812</v>
       </c>
       <c r="C241" t="n">
         <v>662.4199829101562</v>
@@ -6916,11 +6928,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>495.1894226074219</v>
+        <v>495.1893920898438</v>
       </c>
       <c r="C242" t="n">
         <v>498.9200134277344</v>
@@ -6945,7 +6957,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6974,11 +6986,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>429.1469421386719</v>
+        <v>429.14697265625</v>
       </c>
       <c r="C244" t="n">
         <v>432.3800048828125</v>
@@ -7003,7 +7015,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7032,7 +7044,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7061,7 +7073,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7090,7 +7102,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7119,7 +7131,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7148,32 +7160,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>286.7999877929688</v>
+        <v>277.1300048828125</v>
       </c>
       <c r="C250" t="n">
-        <v>286.7999877929688</v>
+        <v>277.1300048828125</v>
       </c>
       <c r="D250" t="n">
-        <v>56976500</v>
+        <v>61529800</v>
       </c>
       <c r="E250" t="n">
         <v>16.46</v>
       </c>
       <c r="F250" t="n">
-        <v>17.42405758158984</v>
+        <v>16.83657380819031</v>
       </c>
       <c r="G250" t="n">
         <v>267236000</v>
       </c>
       <c r="H250" t="n">
-        <v>76643281537.8418</v>
+        <v>74059113984.86328</v>
       </c>
       <c r="I250" t="n">
-        <v>0.2132066787408882</v>
+        <v>0.2302451765480699</v>
       </c>
     </row>
   </sheetData>
@@ -7205,75 +7217,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39661</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39752</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40151</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7309,13 +7321,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39753</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39844</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7351,13 +7363,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39845</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39933</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7393,13 +7405,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7426,7 +7438,7 @@
       <c r="I5" t="n">
         <v>1.35</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="K5" t="n">
@@ -7439,13 +7451,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40151</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7472,7 +7484,7 @@
       <c r="I6" t="n">
         <v>1.3</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="K6" t="n">
@@ -7485,13 +7497,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40118</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7518,7 +7530,7 @@
       <c r="I7" t="n">
         <v>1.39</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="K7" t="n">
@@ -7531,13 +7543,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40210</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7564,7 +7576,7 @@
       <c r="I8" t="n">
         <v>1.7</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="K8" t="n">
@@ -7577,13 +7589,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7610,7 +7622,7 @@
       <c r="I9" t="n">
         <v>1.77</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="K9" t="n">
@@ -7623,13 +7635,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40391</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40482</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7656,7 +7668,7 @@
       <c r="I10" t="n">
         <v>1.76</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="K10" t="n">
@@ -7669,13 +7681,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40483</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7702,7 +7714,7 @@
       <c r="I11" t="n">
         <v>1.64</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="K11" t="n">
@@ -7715,13 +7727,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40575</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7748,7 +7760,7 @@
       <c r="I12" t="n">
         <v>2.06</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="K12" t="n">
@@ -7761,13 +7773,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40664</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40755</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7794,7 +7806,7 @@
       <c r="I13" t="n">
         <v>2.02</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="K13" t="n">
@@ -7807,13 +7819,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40756</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40847</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7840,7 +7852,7 @@
       <c r="I14" t="n">
         <v>2.030000000000001</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="K14" t="n">
@@ -7853,13 +7865,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40848</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7886,7 +7898,7 @@
       <c r="I15" t="n">
         <v>2.19</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K15" t="n">
@@ -7899,13 +7911,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40940</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41029</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7932,7 +7944,7 @@
       <c r="I16" t="n">
         <v>2.41</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="K16" t="n">
@@ -7945,13 +7957,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41030</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41121</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41165</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7978,7 +7990,7 @@
       <c r="I17" t="n">
         <v>2.61</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41165</v>
       </c>
       <c r="K17" t="n">
@@ -7991,13 +8003,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41122</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41213</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41242</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8024,7 +8036,7 @@
       <c r="I18" t="n">
         <v>2.76</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41242</v>
       </c>
       <c r="K18" t="n">
@@ -8037,13 +8049,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41214</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8070,7 +8082,7 @@
       <c r="I19" t="n">
         <v>2.6</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="K19" t="n">
@@ -8083,13 +8095,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41394</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8116,7 +8128,7 @@
       <c r="I20" t="n">
         <v>2.89</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="K20" t="n">
@@ -8129,13 +8141,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41395</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41486</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41530</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8162,7 +8174,7 @@
       <c r="I21" t="n">
         <v>2.830000000000001</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41530</v>
       </c>
       <c r="K21" t="n">
@@ -8175,13 +8187,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41487</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41578</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41600</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8208,7 +8220,7 @@
       <c r="I22" t="n">
         <v>2.85</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41600</v>
       </c>
       <c r="K22" t="n">
@@ -8221,13 +8233,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41579</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8254,7 +8266,7 @@
       <c r="I23" t="n">
         <v>2.49</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="K23" t="n">
@@ -8267,13 +8279,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41671</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41759</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41780</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8300,7 +8312,7 @@
       <c r="I24" t="n">
         <v>3.17</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41780</v>
       </c>
       <c r="K24" t="n">
@@ -8313,13 +8325,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41760</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41851</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41894</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8346,7 +8358,7 @@
       <c r="I25" t="n">
         <v>3.12</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41894</v>
       </c>
       <c r="K25" t="n">
@@ -8359,13 +8371,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41852</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41943</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41964</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8392,7 +8404,7 @@
       <c r="I26" t="n">
         <v>2.87</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41964</v>
       </c>
       <c r="K26" t="n">
@@ -8405,13 +8417,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41944</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8438,7 +8450,7 @@
       <c r="I27" t="n">
         <v>2.77</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="K27" t="n">
@@ -8451,13 +8463,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42036</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42124</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8484,7 +8496,7 @@
       <c r="I28" t="n">
         <v>1.16</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="K28" t="n">
@@ -8497,13 +8509,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8530,7 +8542,7 @@
       <c r="I29" t="n">
         <v>1.31</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="K29" t="n">
@@ -8543,13 +8555,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42217</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42308</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8576,7 +8588,7 @@
       <c r="I30" t="n">
         <v>1.49</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="K30" t="n">
@@ -8589,13 +8601,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42309</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8622,7 +8634,7 @@
       <c r="I31" t="n">
         <v>1.81</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K31" t="n">
@@ -8635,13 +8647,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42401</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8668,7 +8680,7 @@
       <c r="I32" t="n">
         <v>3.97</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="K32" t="n">
@@ -8681,13 +8693,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42491</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42582</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8714,7 +8726,7 @@
       <c r="I33" t="n">
         <v>3.76</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="K33" t="n">
@@ -8727,13 +8739,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42583</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8760,7 +8772,7 @@
       <c r="I34" t="n">
         <v>3.75</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="K34" t="n">
@@ -8773,13 +8785,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42675</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8806,7 +8818,7 @@
       <c r="I35" t="n">
         <v>3.71</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="K35" t="n">
@@ -8819,13 +8831,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42767</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8852,7 +8864,7 @@
       <c r="I36" t="n">
         <v>3.470000000000001</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="K36" t="n">
@@ -8865,13 +8877,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8898,7 +8910,7 @@
       <c r="I37" t="n">
         <v>3.720000000000001</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="K37" t="n">
@@ -8911,13 +8923,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42948</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43039</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8944,7 +8956,7 @@
       <c r="I38" t="n">
         <v>3.77</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="K38" t="n">
@@ -8957,13 +8969,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43040</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8990,7 +9002,7 @@
       <c r="I39" t="n">
         <v>3.640000000000001</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="K39" t="n">
@@ -9003,13 +9015,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43132</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43220</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9036,7 +9048,7 @@
       <c r="I40" t="n">
         <v>4.53</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="K40" t="n">
@@ -9049,13 +9061,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43221</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43312</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9082,7 +9094,7 @@
       <c r="I41" t="n">
         <v>4.62</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="K41" t="n">
@@ -9095,13 +9107,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43313</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43404</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9128,7 +9140,7 @@
       <c r="I42" t="n">
         <v>4.82</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="K42" t="n">
@@ -9141,13 +9153,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43405</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43496</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9174,7 +9186,7 @@
       <c r="I43" t="n">
         <v>5.62</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="K43" t="n">
@@ -9187,13 +9199,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43608</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9220,7 +9232,7 @@
       <c r="I44" t="n">
         <v>6.25</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43608</v>
       </c>
       <c r="K44" t="n">
@@ -9233,13 +9245,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43586</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9266,7 +9278,7 @@
       <c r="I45" t="n">
         <v>5.9</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="K45" t="n">
@@ -9279,13 +9291,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43678</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43790</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9312,7 +9324,7 @@
       <c r="I46" t="n">
         <v>5.99</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43790</v>
       </c>
       <c r="K46" t="n">
@@ -9325,13 +9337,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9358,7 +9370,7 @@
       <c r="I47" t="n">
         <v>6.18</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="K47" t="n">
@@ -9371,13 +9383,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9404,7 +9416,7 @@
       <c r="I48" t="n">
         <v>5.07</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="K48" t="n">
@@ -9417,13 +9429,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9450,7 +9462,7 @@
       <c r="I49" t="n">
         <v>6.92</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="K49" t="n">
@@ -9463,13 +9475,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9496,7 +9508,7 @@
       <c r="I50" t="n">
         <v>7.45</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="K50" t="n">
@@ -9509,13 +9521,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9542,7 +9554,7 @@
       <c r="I51" t="n">
         <v>6.61</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="K51" t="n">
@@ -9555,13 +9567,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9588,7 +9600,7 @@
       <c r="I52" t="n">
         <v>7.8</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="K52" t="n">
@@ -9601,13 +9613,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44447</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9634,7 +9646,7 @@
       <c r="I53" t="n">
         <v>7.56</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44447</v>
       </c>
       <c r="K53" t="n">
@@ -9647,13 +9659,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44518</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9680,7 +9692,7 @@
       <c r="I54" t="n">
         <v>7.63</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44518</v>
       </c>
       <c r="K54" t="n">
@@ -9693,13 +9705,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44622</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9726,7 +9738,7 @@
       <c r="I55" t="n">
         <v>7.909999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44622</v>
       </c>
       <c r="K55" t="n">
@@ -9739,13 +9751,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44593</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44705</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9772,7 +9784,7 @@
       <c r="I56" t="n">
         <v>8.890000000000001</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44705</v>
       </c>
       <c r="K56" t="n">
@@ -9785,13 +9797,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9818,7 +9830,7 @@
       <c r="I57" t="n">
         <v>7.28</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="K57" t="n">
@@ -9831,13 +9843,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9864,7 +9876,7 @@
       <c r="I58" t="n">
         <v>6.6</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="K58" t="n">
@@ -9877,13 +9889,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44866</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9910,7 +9922,7 @@
       <c r="I59" t="n">
         <v>6.850000000000001</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="K59" t="n">
@@ -9923,13 +9935,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44958</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9956,7 +9968,7 @@
       <c r="I60" t="n">
         <v>7.95</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="K60" t="n">
@@ -9969,13 +9981,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="I61" t="n">
         <v>8.420000000000002</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="K61" t="n">
@@ -10015,13 +10027,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45139</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45230</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45258</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10048,7 +10060,7 @@
       <c r="I62" t="n">
         <v>9.130000000000001</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45258</v>
       </c>
       <c r="K62" t="n">
@@ -10061,13 +10073,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45231</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10094,7 +10106,7 @@
       <c r="I63" t="n">
         <v>9.780000000000001</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="K63" t="n">
@@ -10107,13 +10119,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45323</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10140,7 +10152,7 @@
       <c r="I64" t="n">
         <v>10.82</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="K64" t="n">
@@ -10153,13 +10165,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45413</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45504</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45539</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10186,7 +10198,7 @@
       <c r="I65" t="n">
         <v>10.43</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45539</v>
       </c>
       <c r="K65" t="n">
@@ -10199,13 +10211,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45505</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45596</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10232,7 +10244,7 @@
       <c r="I66" t="n">
         <v>10.28</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="K66" t="n">
@@ -10245,13 +10257,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10278,7 +10290,7 @@
       <c r="I67" t="n">
         <v>10.7</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="K67" t="n">
@@ -10291,13 +10303,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45777</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10324,7 +10336,7 @@
       <c r="I68" t="n">
         <v>12.3</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="K68" t="n">
@@ -10337,13 +10349,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45778</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45869</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10370,7 +10382,7 @@
       <c r="I69" t="n">
         <v>13.67</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="K69" t="n">
@@ -10383,13 +10395,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10416,7 +10428,7 @@
       <c r="I70" t="n">
         <v>14.56</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="K70" t="n">
@@ -10429,13 +10441,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10462,7 +10474,7 @@
       <c r="I71" t="n">
         <v>15.37</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="K71" t="n">
@@ -10475,13 +10487,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10508,7 +10520,7 @@
       <c r="I72" t="n">
         <v>16.44</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="K72" t="n">
@@ -10521,13 +10533,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10554,7 +10566,7 @@
       <c r="I73" t="n">
         <v>16.46</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="K73" t="n">
@@ -10591,52 +10603,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40140</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40151</v>
       </c>
       <c r="C2" t="n">
@@ -10665,10 +10677,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40231</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="C3" t="n">
@@ -10697,10 +10709,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40322</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40326</v>
       </c>
       <c r="C4" t="n">
@@ -10729,10 +10741,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40421</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40437</v>
       </c>
       <c r="C5" t="n">
@@ -10761,10 +10773,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40512</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40518</v>
       </c>
       <c r="C6" t="n">
@@ -10793,10 +10805,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40596</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="C7" t="n">
@@ -10825,10 +10837,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40686</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="C8" t="n">
@@ -10857,10 +10869,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40786</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40800</v>
       </c>
       <c r="C9" t="n">
@@ -10889,10 +10901,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40870</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="C10" t="n">
@@ -10921,10 +10933,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40961</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C11" t="n">
@@ -10953,10 +10965,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41047</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41054</v>
       </c>
       <c r="C12" t="n">
@@ -10985,10 +10997,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41152</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41165</v>
       </c>
       <c r="C13" t="n">
@@ -11017,10 +11029,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41233</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41242</v>
       </c>
       <c r="C14" t="n">
@@ -11049,10 +11061,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41327</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="C15" t="n">
@@ -11081,10 +11093,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41417</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41424</v>
       </c>
       <c r="C16" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41516</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41530</v>
       </c>
       <c r="C17" t="n">
@@ -11145,10 +11157,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41596</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41600</v>
       </c>
       <c r="C18" t="n">
@@ -11177,10 +11189,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41687</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41691</v>
       </c>
       <c r="C19" t="n">
@@ -11209,10 +11221,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41773</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41780</v>
       </c>
       <c r="C20" t="n">
@@ -11241,10 +11253,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41880</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41894</v>
       </c>
       <c r="C21" t="n">
@@ -11273,10 +11285,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41957</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41964</v>
       </c>
       <c r="C22" t="n">
@@ -11305,10 +11317,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42052</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42054</v>
       </c>
       <c r="C23" t="n">
@@ -11337,10 +11349,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42142</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42146</v>
       </c>
       <c r="C24" t="n">
@@ -11369,10 +11381,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42240</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42248</v>
       </c>
       <c r="C25" t="n">
@@ -11401,10 +11413,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42324</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42328</v>
       </c>
       <c r="C26" t="n">
@@ -11433,10 +11445,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42419</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C27" t="n">
@@ -11465,10 +11477,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42508</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42514</v>
       </c>
       <c r="C28" t="n">
@@ -11497,10 +11509,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42607</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42614</v>
       </c>
       <c r="C29" t="n">
@@ -11529,10 +11541,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42688</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42692</v>
       </c>
       <c r="C30" t="n">
@@ -11561,10 +11573,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42783</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42789</v>
       </c>
       <c r="C31" t="n">
@@ -11593,10 +11605,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42872</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42878</v>
       </c>
       <c r="C32" t="n">
@@ -11625,10 +11637,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42972</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42979</v>
       </c>
       <c r="C33" t="n">
@@ -11657,10 +11669,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43053</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43059</v>
       </c>
       <c r="C34" t="n">
@@ -11689,10 +11701,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43147</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43153</v>
       </c>
       <c r="C35" t="n">
@@ -11721,10 +11733,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43236</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43242</v>
       </c>
       <c r="C36" t="n">
@@ -11753,10 +11765,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43336</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="C37" t="n">
@@ -11785,10 +11797,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43418</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43424</v>
       </c>
       <c r="C38" t="n">
@@ -11817,10 +11829,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43518</v>
       </c>
       <c r="C39" t="n">
@@ -11849,10 +11861,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43602</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43608</v>
       </c>
       <c r="C40" t="n">
@@ -11881,10 +11893,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43700</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43707</v>
       </c>
       <c r="C41" t="n">
@@ -11913,10 +11925,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43784</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43790</v>
       </c>
       <c r="C42" t="n">
@@ -11945,10 +11957,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43879</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="C43" t="n">
@@ -11977,10 +11989,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43966</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43972</v>
       </c>
       <c r="C44" t="n">
@@ -12009,10 +12021,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44067</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="C45" t="n">
@@ -12041,10 +12053,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44148</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44154</v>
       </c>
       <c r="C46" t="n">
@@ -12073,10 +12085,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44243</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44250</v>
       </c>
       <c r="C47" t="n">
@@ -12105,10 +12117,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44335</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44341</v>
       </c>
       <c r="C48" t="n">
@@ -12137,10 +12149,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44439</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44447</v>
       </c>
       <c r="C49" t="n">
@@ -12169,10 +12181,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44512</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44518</v>
       </c>
       <c r="C50" t="n">
@@ -12201,10 +12213,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44622</v>
       </c>
       <c r="C51" t="n">
@@ -12233,10 +12245,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44699</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44705</v>
       </c>
       <c r="C52" t="n">
@@ -12265,10 +12277,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44799</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44806</v>
       </c>
       <c r="C53" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44886</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44894</v>
       </c>
       <c r="C54" t="n">
@@ -12329,10 +12341,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44973</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44980</v>
       </c>
       <c r="C55" t="n">
@@ -12361,10 +12373,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45062</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45069</v>
       </c>
       <c r="C56" t="n">
@@ -12393,10 +12405,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45163</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="C57" t="n">
@@ -12425,10 +12437,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45250</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45258</v>
       </c>
       <c r="C58" t="n">
@@ -12457,10 +12469,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45337</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45344</v>
       </c>
       <c r="C59" t="n">
@@ -12489,10 +12501,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45428</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45435</v>
       </c>
       <c r="C60" t="n">
@@ -12521,10 +12533,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45531</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45539</v>
       </c>
       <c r="C61" t="n">
@@ -12553,10 +12565,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45610</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45617</v>
       </c>
       <c r="C62" t="n">
@@ -12585,10 +12597,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45707</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45713</v>
       </c>
       <c r="C63" t="n">
@@ -12617,10 +12629,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45792</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45799</v>
       </c>
       <c r="C64" t="n">
@@ -12649,10 +12661,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45895</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45903</v>
       </c>
       <c r="C65" t="n">
@@ -12681,10 +12693,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45974</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45981</v>
       </c>
       <c r="C66" t="n">
@@ -12713,10 +12725,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46073</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46079</v>
       </c>
       <c r="C67" t="n">
@@ -12745,10 +12757,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46156</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46162</v>
       </c>
       <c r="C68" t="n">
@@ -12777,10 +12789,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46265</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46274</v>
       </c>
       <c r="C69" t="n">
@@ -12827,12 +12839,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/INTU.xlsx
+++ b/salidas/empresas/INTU.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>22.87910079956055</v>
+        <v>22.87909126281738</v>
       </c>
       <c r="C2" t="n">
         <v>26.16500091552734</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>23.25509452819824</v>
+        <v>23.25508689880371</v>
       </c>
       <c r="C4" t="n">
         <v>26.59499931335449</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>23.68354606628418</v>
+        <v>23.68355369567871</v>
       </c>
       <c r="C5" t="n">
         <v>27.08499908447266</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>24.17323684692383</v>
+        <v>24.1732234954834</v>
       </c>
       <c r="C6" t="n">
         <v>27.64500045776367</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>26.46857261657715</v>
+        <v>26.46857452392578</v>
       </c>
       <c r="C7" t="n">
         <v>30.27000045776367</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>26.99322319030762</v>
+        <v>26.99321556091309</v>
       </c>
       <c r="C8" t="n">
         <v>30.8700008392334</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>28.06001281738281</v>
+        <v>28.06000900268555</v>
       </c>
       <c r="C10" t="n">
         <v>32.09000015258789</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>30.86686134338379</v>
+        <v>30.86689567565918</v>
       </c>
       <c r="C11" t="n">
         <v>35.29999923706055</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>27.56159210205078</v>
+        <v>27.56159019470215</v>
       </c>
       <c r="C12" t="n">
         <v>31.52000045776367</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>26.67842483520508</v>
+        <v>26.67843246459961</v>
       </c>
       <c r="C13" t="n">
         <v>30.51000022888184</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>27.50039100646973</v>
+        <v>27.50038528442383</v>
       </c>
       <c r="C14" t="n">
         <v>31.45000076293945</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>25.80401611328125</v>
+        <v>25.80401039123535</v>
       </c>
       <c r="C15" t="n">
         <v>29.51000022888184</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>23.92401695251465</v>
+        <v>23.92402267456055</v>
       </c>
       <c r="C16" t="n">
         <v>27.36000061035156</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>24.87713241577148</v>
+        <v>24.87713623046875</v>
       </c>
       <c r="C17" t="n">
         <v>28.45000076293945</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>26.669677734375</v>
+        <v>26.66968154907227</v>
       </c>
       <c r="C18" t="n">
         <v>30.5</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>26.30243301391602</v>
+        <v>26.30242729187012</v>
       </c>
       <c r="C19" t="n">
         <v>30.07999992370605</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>25.04327011108398</v>
+        <v>25.04327774047852</v>
       </c>
       <c r="C20" t="n">
         <v>28.63999938964844</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>23.88029861450195</v>
+        <v>23.88030433654785</v>
       </c>
       <c r="C21" t="n">
         <v>27.30999946594238</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>26.49480438232422</v>
+        <v>26.49480056762695</v>
       </c>
       <c r="C22" t="n">
         <v>30.29999923706055</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>28.12995910644531</v>
+        <v>28.12996101379395</v>
       </c>
       <c r="C23" t="n">
         <v>32.16999816894531</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>25.63787841796875</v>
+        <v>25.63787651062012</v>
       </c>
       <c r="C24" t="n">
         <v>29.31999969482422</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>27.64029312133789</v>
+        <v>27.64028358459473</v>
       </c>
       <c r="C25" t="n">
         <v>31.61000061035156</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>26.83582496643066</v>
+        <v>26.8358268737793</v>
       </c>
       <c r="C26" t="n">
         <v>30.69000053405762</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>23.22449111938477</v>
+        <v>23.2244873046875</v>
       </c>
       <c r="C27" t="n">
         <v>26.55999946594238</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>23.61797142028809</v>
+        <v>23.61797904968262</v>
       </c>
       <c r="C28" t="n">
         <v>27.01000022888184</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>23.5829906463623</v>
+        <v>23.58299827575684</v>
       </c>
       <c r="C29" t="n">
         <v>26.96999931335449</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>25.32309150695801</v>
+        <v>25.32307815551758</v>
       </c>
       <c r="C30" t="n">
         <v>28.95999908447266</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>24.10764694213867</v>
+        <v>24.10764503479004</v>
       </c>
       <c r="C31" t="n">
         <v>27.56999969482422</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>23.89778518676758</v>
+        <v>23.89778327941895</v>
       </c>
       <c r="C32" t="n">
         <v>27.32999992370605</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>26.29368019104004</v>
+        <v>26.29368591308594</v>
       </c>
       <c r="C33" t="n">
         <v>30.06999969482422</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>27.64029312133789</v>
+        <v>27.64028358459473</v>
       </c>
       <c r="C34" t="n">
         <v>31.61000061035156</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>21.91285514831543</v>
+        <v>21.91286087036133</v>
       </c>
       <c r="C35" t="n">
         <v>25.05999946594238</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>19.37705612182617</v>
+        <v>19.37704658508301</v>
       </c>
       <c r="C36" t="n">
         <v>22.15999984741211</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>20.8023567199707</v>
+        <v>20.80236053466797</v>
       </c>
       <c r="C37" t="n">
         <v>23.79000091552734</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>19.8055248260498</v>
+        <v>19.80551910400391</v>
       </c>
       <c r="C38" t="n">
         <v>22.64999961853027</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>23.60922813415527</v>
+        <v>23.60923385620117</v>
       </c>
       <c r="C40" t="n">
         <v>27</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>20.22524261474609</v>
+        <v>20.2252368927002</v>
       </c>
       <c r="C41" t="n">
         <v>23.1299991607666</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>23.80159950256348</v>
+        <v>23.80160140991211</v>
       </c>
       <c r="C42" t="n">
         <v>27.21999931335449</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>24.64978408813477</v>
+        <v>24.6497917175293</v>
       </c>
       <c r="C43" t="n">
         <v>28.19000053405762</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>25.97015953063965</v>
+        <v>25.97015190124512</v>
       </c>
       <c r="C44" t="n">
         <v>29.70000076293945</v>
@@ -1315,7 +1315,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>24.28253173828125</v>
+        <v>24.28253555297852</v>
       </c>
       <c r="C45" t="n">
         <v>27.77000045776367</v>
@@ -1334,7 +1334,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>24.92085838317871</v>
+        <v>24.92085266113281</v>
       </c>
       <c r="C46" t="n">
         <v>28.5</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>25.41927146911621</v>
+        <v>25.41926765441895</v>
       </c>
       <c r="C47" t="n">
         <v>29.06999969482422</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>25.54168701171875</v>
+        <v>25.54168891906738</v>
       </c>
       <c r="C48" t="n">
         <v>29.20999908447266</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>26.87080192565918</v>
+        <v>26.87079811096191</v>
       </c>
       <c r="C49" t="n">
         <v>30.72999954223633</v>
@@ -1416,7 +1416,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>25.89145851135254</v>
+        <v>25.8914623260498</v>
       </c>
       <c r="C50" t="n">
         <v>29.61000061035156</v>
@@ -1491,7 +1491,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>31.64511108398438</v>
+        <v>31.64510154724121</v>
       </c>
       <c r="C53" t="n">
         <v>36.18999862670898</v>
@@ -1516,7 +1516,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>31.25163841247559</v>
+        <v>31.25163078308105</v>
       </c>
       <c r="C54" t="n">
         <v>35.7400016784668</v>
@@ -1541,7 +1541,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>30.40345191955566</v>
+        <v>30.4034481048584</v>
       </c>
       <c r="C55" t="n">
         <v>34.77000045776367</v>
@@ -1566,7 +1566,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>34.75802612304688</v>
+        <v>34.75802993774414</v>
       </c>
       <c r="C56" t="n">
         <v>39.75</v>
@@ -1591,7 +1591,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>37.37253952026367</v>
+        <v>37.37253189086914</v>
       </c>
       <c r="C57" t="n">
         <v>42.7400016784668</v>
@@ -1616,7 +1616,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>38.30817031860352</v>
+        <v>38.30816268920898</v>
       </c>
       <c r="C58" t="n">
         <v>43.81000137329102</v>
@@ -1645,7 +1645,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>41.95447158813477</v>
+        <v>41.95448303222656</v>
       </c>
       <c r="C59" t="n">
         <v>47.97999954223633</v>
@@ -1674,7 +1674,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>39.25252914428711</v>
+        <v>39.25252532958984</v>
       </c>
       <c r="C60" t="n">
         <v>44.88999938964844</v>
@@ -1703,7 +1703,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>43.10870361328125</v>
+        <v>43.10869979858398</v>
       </c>
       <c r="C61" t="n">
         <v>49.29999923706055</v>
@@ -1732,7 +1732,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>41.03632736206055</v>
+        <v>41.03634262084961</v>
       </c>
       <c r="C62" t="n">
         <v>46.93000030517578</v>
@@ -1790,7 +1790,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>46.44022369384766</v>
+        <v>46.44021606445312</v>
       </c>
       <c r="C64" t="n">
         <v>53.11000061035156</v>
@@ -1819,7 +1819,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>48.58254623413086</v>
+        <v>48.5825309753418</v>
       </c>
       <c r="C65" t="n">
         <v>55.56000137329102</v>
@@ -1869,7 +1869,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>45.34721374511719</v>
+        <v>45.34719848632812</v>
       </c>
       <c r="C67" t="n">
         <v>51.86000061035156</v>
@@ -1894,7 +1894,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>40.83523178100586</v>
+        <v>40.83522033691406</v>
       </c>
       <c r="C68" t="n">
         <v>46.70000076293945</v>
@@ -1944,7 +1944,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>41.48229598999023</v>
+        <v>41.4822883605957</v>
       </c>
       <c r="C70" t="n">
         <v>47.43999862670898</v>
@@ -1973,7 +1973,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>47.08047485351562</v>
+        <v>47.08049011230469</v>
       </c>
       <c r="C71" t="n">
         <v>53.66999816894531</v>
@@ -2002,7 +2002,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>46.70327377319336</v>
+        <v>46.70327758789062</v>
       </c>
       <c r="C72" t="n">
         <v>53.2400016784668</v>
@@ -2031,7 +2031,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>46.13307571411133</v>
+        <v>46.13307952880859</v>
       </c>
       <c r="C73" t="n">
         <v>52.59000015258789</v>
@@ -2060,7 +2060,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>49.65213394165039</v>
+        <v>49.65212631225586</v>
       </c>
       <c r="C74" t="n">
         <v>56.43999862670898</v>
@@ -2089,7 +2089,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>50.88376998901367</v>
+        <v>50.88376617431641</v>
       </c>
       <c r="C75" t="n">
         <v>57.84000015258789</v>
@@ -2118,7 +2118,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>52.92474746704102</v>
+        <v>52.92474365234375</v>
       </c>
       <c r="C76" t="n">
         <v>60.15999984741211</v>
@@ -2147,7 +2147,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>51.12728118896484</v>
+        <v>51.12728500366211</v>
       </c>
       <c r="C77" t="n">
         <v>57.97000122070312</v>
@@ -2176,7 +2176,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>49.59268188476562</v>
+        <v>49.59267044067383</v>
       </c>
       <c r="C78" t="n">
         <v>56.22999954223633</v>
@@ -2205,7 +2205,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>52.34439086914062</v>
+        <v>52.34439468383789</v>
       </c>
       <c r="C79" t="n">
         <v>59.34999847412109</v>
@@ -2234,7 +2234,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>51.29982757568359</v>
+        <v>51.29978561401367</v>
       </c>
       <c r="C80" t="n">
         <v>58.02000045776367</v>
@@ -2263,7 +2263,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>51.75957489013672</v>
+        <v>51.75957870483398</v>
       </c>
       <c r="C81" t="n">
         <v>58.54000091552734</v>
@@ -2292,7 +2292,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>52.06018829345703</v>
+        <v>52.0601921081543</v>
       </c>
       <c r="C82" t="n">
         <v>58.88000106811523</v>
@@ -2321,7 +2321,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>52.69316101074219</v>
+        <v>52.69317626953125</v>
       </c>
       <c r="C83" t="n">
         <v>59.43000030517578</v>
@@ -2379,7 +2379,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>52.73749542236328</v>
+        <v>52.73749923706055</v>
       </c>
       <c r="C85" t="n">
         <v>59.47999954223633</v>
@@ -2408,7 +2408,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>55.46012496948242</v>
+        <v>55.46012115478516</v>
       </c>
       <c r="C86" t="n">
         <v>62.38000106811523</v>
@@ -2437,7 +2437,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>57.31827545166016</v>
+        <v>57.31827163696289</v>
       </c>
       <c r="C87" t="n">
         <v>64.47000122070312</v>
@@ -2466,7 +2466,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>58.37627410888672</v>
+        <v>58.37627792358398</v>
       </c>
       <c r="C88" t="n">
         <v>65.66000366210938</v>
@@ -2495,7 +2495,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>53.16429138183594</v>
+        <v>53.16428375244141</v>
       </c>
       <c r="C89" t="n">
         <v>59.63999938964844</v>
@@ -2524,7 +2524,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>52.09458923339844</v>
+        <v>52.09457397460938</v>
       </c>
       <c r="C90" t="n">
         <v>58.43999862670898</v>
@@ -2553,7 +2553,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>54.41226959228516</v>
+        <v>54.41227340698242</v>
       </c>
       <c r="C91" t="n">
         <v>61.04000091552734</v>
@@ -2582,7 +2582,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>57.13484573364258</v>
+        <v>57.13483810424805</v>
       </c>
       <c r="C92" t="n">
         <v>63.91999816894531</v>
@@ -2611,7 +2611,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>56.7862434387207</v>
+        <v>56.78624725341797</v>
       </c>
       <c r="C93" t="n">
         <v>63.52999877929688</v>
@@ -2640,7 +2640,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>59.27115249633789</v>
+        <v>59.27114105224609</v>
       </c>
       <c r="C94" t="n">
         <v>66.30999755859375</v>
@@ -2669,7 +2669,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>64.013427734375</v>
+        <v>64.01337432861328</v>
       </c>
       <c r="C95" t="n">
         <v>71.41000366210938</v>
@@ -2698,7 +2698,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>66.54128265380859</v>
+        <v>66.54130554199219</v>
       </c>
       <c r="C96" t="n">
         <v>74.23000335693359</v>
@@ -2727,7 +2727,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>68.41482543945312</v>
+        <v>68.41481018066406</v>
       </c>
       <c r="C97" t="n">
         <v>76.31999969482422</v>
@@ -2785,7 +2785,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>70.22842407226562</v>
+        <v>70.22840881347656</v>
       </c>
       <c r="C99" t="n">
         <v>78.15000152587891</v>
@@ -2843,7 +2843,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>68.24507904052734</v>
+        <v>68.24506378173828</v>
       </c>
       <c r="C101" t="n">
         <v>75.75</v>
@@ -2872,7 +2872,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>71.43431854248047</v>
+        <v>71.43433380126953</v>
       </c>
       <c r="C102" t="n">
         <v>79.29000091552734</v>
@@ -2901,7 +2901,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>72.55148315429688</v>
+        <v>72.55147552490234</v>
       </c>
       <c r="C103" t="n">
         <v>80.52999877929688</v>
@@ -2930,7 +2930,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.02197265625</v>
+        <v>74.02201080322266</v>
       </c>
       <c r="C104" t="n">
         <v>81.97000122070312</v>
@@ -2959,7 +2959,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>75.11465454101562</v>
+        <v>75.11463165283203</v>
       </c>
       <c r="C105" t="n">
         <v>83.18000030517578</v>
@@ -2988,7 +2988,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>79.15123748779297</v>
+        <v>79.15122985839844</v>
       </c>
       <c r="C106" t="n">
         <v>87.65000152587891</v>
@@ -3046,7 +3046,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>85.02589416503906</v>
+        <v>85.02586364746094</v>
       </c>
       <c r="C108" t="n">
         <v>93.87000274658203</v>
@@ -3075,7 +3075,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>83.504150390625</v>
+        <v>83.50416564941406</v>
       </c>
       <c r="C109" t="n">
         <v>92.19000244140625</v>
@@ -3104,7 +3104,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>78.86399841308594</v>
+        <v>78.86399078369141</v>
       </c>
       <c r="C110" t="n">
         <v>86.81999969482422</v>
@@ -3133,7 +3133,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>88.68337249755859</v>
+        <v>88.68338775634766</v>
       </c>
       <c r="C111" t="n">
         <v>97.62999725341797</v>
@@ -3162,7 +3162,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>88.07478332519531</v>
+        <v>88.07477569580078</v>
       </c>
       <c r="C112" t="n">
         <v>96.95999908447266</v>
@@ -3191,7 +3191,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>91.37062072753906</v>
+        <v>91.37060546875</v>
       </c>
       <c r="C113" t="n">
         <v>100.3300018310547</v>
@@ -3220,7 +3220,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>94.84947967529297</v>
+        <v>94.84950256347656</v>
       </c>
       <c r="C114" t="n">
         <v>104.1500015258789</v>
@@ -3249,7 +3249,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>91.77133178710938</v>
+        <v>91.77130889892578</v>
       </c>
       <c r="C115" t="n">
         <v>100.7699966430664</v>
@@ -3307,7 +3307,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>78.28153991699219</v>
+        <v>78.28153228759766</v>
       </c>
       <c r="C117" t="n">
         <v>85.75</v>
@@ -3336,7 +3336,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>81.02022552490234</v>
+        <v>81.020263671875</v>
       </c>
       <c r="C118" t="n">
         <v>88.75</v>
@@ -3365,7 +3365,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>89.23908233642578</v>
+        <v>89.23906707763672</v>
       </c>
       <c r="C119" t="n">
         <v>97.43000030517578</v>
@@ -3394,7 +3394,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>91.77618408203125</v>
+        <v>91.77619171142578</v>
       </c>
       <c r="C120" t="n">
         <v>100.1999969482422</v>
@@ -3423,7 +3423,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>88.38726806640625</v>
+        <v>88.38725280761719</v>
       </c>
       <c r="C121" t="n">
         <v>96.5</v>
@@ -3452,7 +3452,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>87.75390625</v>
+        <v>87.75386810302734</v>
       </c>
       <c r="C122" t="n">
         <v>95.51000213623047</v>
@@ -3481,7 +3481,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>88.79209899902344</v>
+        <v>88.79212951660156</v>
       </c>
       <c r="C123" t="n">
         <v>96.63999938964844</v>
@@ -3510,7 +3510,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>95.56362152099609</v>
+        <v>95.56360626220703</v>
       </c>
       <c r="C124" t="n">
         <v>104.0100021362305</v>
@@ -3539,7 +3539,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>92.96227264404297</v>
+        <v>92.9622802734375</v>
       </c>
       <c r="C125" t="n">
         <v>100.8899993896484</v>
@@ -3597,7 +3597,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>102.8399353027344</v>
+        <v>102.8399124145508</v>
       </c>
       <c r="C127" t="n">
         <v>111.6100006103516</v>
@@ -3626,7 +3626,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>102.5379028320312</v>
+        <v>102.5378799438477</v>
       </c>
       <c r="C128" t="n">
         <v>110.9899978637695</v>
@@ -3655,7 +3655,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>102.9628448486328</v>
+        <v>102.9628295898438</v>
       </c>
       <c r="C129" t="n">
         <v>111.4499969482422</v>
@@ -3684,7 +3684,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>101.6325225830078</v>
+        <v>101.6325302124023</v>
       </c>
       <c r="C130" t="n">
         <v>110.0100021362305</v>
@@ -3713,7 +3713,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>100.7724761962891</v>
+        <v>100.7724990844727</v>
       </c>
       <c r="C131" t="n">
         <v>108.7399978637695</v>
@@ -3742,7 +3742,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>105.3505401611328</v>
+        <v>105.3505172729492</v>
       </c>
       <c r="C132" t="n">
         <v>113.6800003051758</v>
@@ -3771,7 +3771,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>106.2123947143555</v>
+        <v>106.2124252319336</v>
       </c>
       <c r="C133" t="n">
         <v>114.6100006103516</v>
@@ -3800,7 +3800,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>110.2154235839844</v>
+        <v>110.2154083251953</v>
       </c>
       <c r="C134" t="n">
         <v>118.5800018310547</v>
@@ -3829,7 +3829,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>116.5915069580078</v>
+        <v>116.5915145874023</v>
       </c>
       <c r="C135" t="n">
         <v>125.4400024414062</v>
@@ -3887,7 +3887,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>116.7182312011719</v>
+        <v>116.7182159423828</v>
       </c>
       <c r="C137" t="n">
         <v>125.2099990844727</v>
@@ -3916,7 +3916,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>131.1017608642578</v>
+        <v>131.1017456054688</v>
       </c>
       <c r="C138" t="n">
         <v>140.6399993896484</v>
@@ -3945,7 +3945,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>123.8027572631836</v>
+        <v>123.8028030395508</v>
       </c>
       <c r="C139" t="n">
         <v>132.8099975585938</v>
@@ -4032,7 +4032,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>132.8422546386719</v>
+        <v>132.8422698974609</v>
       </c>
       <c r="C142" t="n">
         <v>142.1399993896484</v>
@@ -4061,7 +4061,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>141.5277404785156</v>
+        <v>141.5278472900391</v>
       </c>
       <c r="C143" t="n">
         <v>151.0200042724609</v>
@@ -4119,7 +4119,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>147.8628692626953</v>
+        <v>147.8628540039062</v>
       </c>
       <c r="C145" t="n">
         <v>157.7799987792969</v>
@@ -4148,7 +4148,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>157.7213592529297</v>
+        <v>157.7213287353516</v>
       </c>
       <c r="C146" t="n">
         <v>167.8999938964844</v>
@@ -4177,7 +4177,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>156.7444152832031</v>
+        <v>156.7444000244141</v>
       </c>
       <c r="C147" t="n">
         <v>166.8600006103516</v>
@@ -4206,7 +4206,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>162.8409729003906</v>
+        <v>162.8410034179688</v>
       </c>
       <c r="C148" t="n">
         <v>173.3500061035156</v>
@@ -4235,7 +4235,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>173.9920654296875</v>
+        <v>173.9921722412109</v>
       </c>
       <c r="C149" t="n">
         <v>184.7899932861328</v>
@@ -4264,7 +4264,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>189.81982421875</v>
+        <v>189.8198699951172</v>
       </c>
       <c r="C150" t="n">
         <v>201.6000061035156</v>
@@ -4293,7 +4293,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>192.3714904785156</v>
+        <v>192.3715057373047</v>
       </c>
       <c r="C151" t="n">
         <v>204.3099975585938</v>
@@ -4322,7 +4322,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>192.6666107177734</v>
+        <v>192.6665954589844</v>
       </c>
       <c r="C152" t="n">
         <v>204.2400054931641</v>
@@ -4351,7 +4351,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>207.0335540771484</v>
+        <v>207.0335845947266</v>
       </c>
       <c r="C153" t="n">
         <v>219.4700012207031</v>
@@ -4380,7 +4380,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>214.5142364501953</v>
+        <v>214.5142211914062</v>
       </c>
       <c r="C154" t="n">
         <v>227.3999938964844</v>
@@ -4409,7 +4409,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>199.4749145507812</v>
+        <v>199.4748687744141</v>
       </c>
       <c r="C155" t="n">
         <v>211</v>
@@ -4438,7 +4438,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>202.8121185302734</v>
+        <v>202.8120880126953</v>
       </c>
       <c r="C156" t="n">
         <v>214.5299987792969</v>
@@ -4467,7 +4467,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>186.0977935791016</v>
+        <v>186.0977783203125</v>
       </c>
       <c r="C157" t="n">
         <v>196.8500061035156</v>
@@ -4496,7 +4496,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>204.5033721923828</v>
+        <v>204.5033416748047</v>
       </c>
       <c r="C158" t="n">
         <v>215.8200073242188</v>
@@ -4525,7 +4525,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>234.1715698242188</v>
+        <v>234.1715850830078</v>
       </c>
       <c r="C159" t="n">
         <v>247.1300048828125</v>
@@ -4554,7 +4554,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>247.7028350830078</v>
+        <v>247.7028198242188</v>
       </c>
       <c r="C160" t="n">
         <v>261.4100036621094</v>
@@ -4612,7 +4612,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>232.4300689697266</v>
+        <v>232.4301300048828</v>
       </c>
       <c r="C162" t="n">
         <v>244.8500061035156</v>
@@ -4670,7 +4670,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>263.7006225585938</v>
+        <v>263.70068359375</v>
       </c>
       <c r="C164" t="n">
         <v>277.3099975585938</v>
@@ -4699,7 +4699,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>274.2084045410156</v>
+        <v>274.2083435058594</v>
       </c>
       <c r="C165" t="n">
         <v>288.3599853515625</v>
@@ -4728,7 +4728,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>252.8886871337891</v>
+        <v>252.8887634277344</v>
       </c>
       <c r="C166" t="n">
         <v>265.9400024414062</v>
@@ -4786,7 +4786,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>246.6856079101562</v>
+        <v>246.6856384277344</v>
       </c>
       <c r="C168" t="n">
         <v>258.8900146484375</v>
@@ -4815,7 +4815,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>249.5822601318359</v>
+        <v>249.5823059082031</v>
       </c>
       <c r="C169" t="n">
         <v>261.9299926757812</v>
@@ -4873,7 +4873,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>253.8105010986328</v>
+        <v>253.8104553222656</v>
       </c>
       <c r="C171" t="n">
         <v>265.8500061035156</v>
@@ -4902,7 +4902,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>219.5840301513672</v>
+        <v>219.5839996337891</v>
       </c>
       <c r="C172" t="n">
         <v>230</v>
@@ -4931,7 +4931,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>258.1473999023438</v>
+        <v>258.1474609375</v>
       </c>
       <c r="C173" t="n">
         <v>269.8099975585938</v>
@@ -4960,7 +4960,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>277.7708435058594</v>
+        <v>277.7709045410156</v>
       </c>
       <c r="C174" t="n">
         <v>290.3200073242188</v>
@@ -4989,7 +4989,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>283.38720703125</v>
+        <v>283.3871765136719</v>
       </c>
       <c r="C175" t="n">
         <v>296.1900024414062</v>
@@ -5018,7 +5018,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>293.6285400390625</v>
+        <v>293.6285095214844</v>
       </c>
       <c r="C176" t="n">
         <v>306.3699951171875</v>
@@ -5105,7 +5105,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>302.125244140625</v>
+        <v>302.1251220703125</v>
       </c>
       <c r="C179" t="n">
         <v>314.6799926757812</v>
@@ -5163,7 +5163,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>364.6951599121094</v>
+        <v>364.6951904296875</v>
       </c>
       <c r="C181" t="n">
         <v>379.8500061035156</v>
@@ -5250,7 +5250,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>368.3665161132812</v>
+        <v>368.3666076660156</v>
       </c>
       <c r="C184" t="n">
         <v>383.0599975585938</v>
@@ -5279,7 +5279,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>396.9197082519531</v>
+        <v>396.9197387695312</v>
       </c>
       <c r="C185" t="n">
         <v>412.1600036621094</v>
@@ -5308,7 +5308,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>422.8539733886719</v>
+        <v>422.8539123535156</v>
       </c>
       <c r="C186" t="n">
         <v>439.0899963378906</v>
@@ -5337,7 +5337,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>472.0451965332031</v>
+        <v>472.0452575683594</v>
       </c>
       <c r="C187" t="n">
         <v>490.1700134277344</v>
@@ -5366,7 +5366,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>510.9690551757812</v>
+        <v>510.9690856933594</v>
       </c>
       <c r="C188" t="n">
         <v>529.969970703125</v>
@@ -5424,7 +5424,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>520.1671142578125</v>
+        <v>520.1671752929688</v>
       </c>
       <c r="C190" t="n">
         <v>539.510009765625</v>
@@ -5453,7 +5453,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>604.3152465820312</v>
+        <v>604.3153686523438</v>
       </c>
       <c r="C191" t="n">
         <v>625.989990234375</v>
@@ -5540,7 +5540,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>536.627685546875</v>
+        <v>536.6276245117188</v>
       </c>
       <c r="C194" t="n">
         <v>555.22998046875</v>
@@ -5569,7 +5569,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>458.4767761230469</v>
+        <v>458.4767456054688</v>
       </c>
       <c r="C195" t="n">
         <v>474.3699951171875</v>
@@ -5598,7 +5598,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>464.7300109863281</v>
+        <v>464.72998046875</v>
       </c>
       <c r="C196" t="n">
         <v>480.8399963378906</v>
@@ -5656,7 +5656,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>401.1249694824219</v>
+        <v>401.125</v>
       </c>
       <c r="C198" t="n">
         <v>414.4599914550781</v>
@@ -5685,7 +5685,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>373.0386657714844</v>
+        <v>373.0386962890625</v>
       </c>
       <c r="C199" t="n">
         <v>385.4400024414062</v>
@@ -5714,7 +5714,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>442.2250366210938</v>
+        <v>442.2249450683594</v>
       </c>
       <c r="C200" t="n">
         <v>456.1700134277344</v>
@@ -5743,7 +5743,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>418.5805969238281</v>
+        <v>418.5805358886719</v>
       </c>
       <c r="C201" t="n">
         <v>431.7799987792969</v>
@@ -5772,7 +5772,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>375.479736328125</v>
+        <v>375.4797058105469</v>
       </c>
       <c r="C202" t="n">
         <v>387.3200073242188</v>
@@ -5801,7 +5801,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>415.2145080566406</v>
+        <v>415.2144470214844</v>
       </c>
       <c r="C203" t="n">
         <v>427.5</v>
@@ -5859,7 +5859,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>378.0346374511719</v>
+        <v>378.0345764160156</v>
       </c>
       <c r="C205" t="n">
         <v>389.2200012207031</v>
@@ -5888,7 +5888,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>411.3534240722656</v>
+        <v>411.3533630371094</v>
       </c>
       <c r="C206" t="n">
         <v>422.6700134277344</v>
@@ -5917,7 +5917,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>396.2781066894531</v>
+        <v>396.2781372070312</v>
       </c>
       <c r="C207" t="n">
         <v>407.1799926757812</v>
@@ -5946,7 +5946,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>433.8932800292969</v>
+        <v>433.8933715820312</v>
       </c>
       <c r="C208" t="n">
         <v>445.8299865722656</v>
@@ -6033,7 +6033,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>446.7158508300781</v>
+        <v>446.7158203125</v>
       </c>
       <c r="C211" t="n">
         <v>458.1900024414062</v>
@@ -6062,7 +6062,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>499.7491455078125</v>
+        <v>499.7491760253906</v>
       </c>
       <c r="C212" t="n">
         <v>511.7000122070312</v>
@@ -6091,7 +6091,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>529.1559448242188</v>
+        <v>529.1560668945312</v>
       </c>
       <c r="C213" t="n">
         <v>541.8099975585938</v>
@@ -6120,7 +6120,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>499.0068969726562</v>
+        <v>499.0069580078125</v>
       </c>
       <c r="C214" t="n">
         <v>510.9400024414062</v>
@@ -6149,7 +6149,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>484.2325744628906</v>
+        <v>484.2326049804688</v>
       </c>
       <c r="C215" t="n">
         <v>494.9500122070312</v>
@@ -6207,7 +6207,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>611.4959106445312</v>
+        <v>611.495849609375</v>
       </c>
       <c r="C217" t="n">
         <v>625.030029296875</v>
@@ -6236,7 +6236,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>618.5897827148438</v>
+        <v>618.5899047851562</v>
       </c>
       <c r="C218" t="n">
         <v>631.3300170898438</v>
@@ -6265,7 +6265,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>649.512939453125</v>
+        <v>649.5130004882812</v>
       </c>
       <c r="C219" t="n">
         <v>662.8900146484375</v>
@@ -6352,7 +6352,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>565.5964965820312</v>
+        <v>565.596435546875</v>
       </c>
       <c r="C222" t="n">
         <v>576.4400024414062</v>
@@ -6381,7 +6381,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>644.8471069335938</v>
+        <v>644.846923828125</v>
       </c>
       <c r="C223" t="n">
         <v>657.2100219726562</v>
@@ -6410,7 +6410,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>636.0526123046875</v>
+        <v>636.0525512695312</v>
       </c>
       <c r="C224" t="n">
         <v>647.3499755859375</v>
@@ -6439,7 +6439,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>619.2608032226562</v>
+        <v>619.2608642578125</v>
       </c>
       <c r="C225" t="n">
         <v>630.260009765625</v>
@@ -6468,7 +6468,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>610.162353515625</v>
+        <v>610.1624145507812</v>
       </c>
       <c r="C226" t="n">
         <v>621</v>
@@ -6497,7 +6497,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>600.6541748046875</v>
+        <v>600.6541137695312</v>
       </c>
       <c r="C227" t="n">
         <v>610.2999877929688</v>
@@ -6526,7 +6526,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>631.58740234375</v>
+        <v>631.5873413085938</v>
       </c>
       <c r="C228" t="n">
         <v>641.72998046875</v>
@@ -6700,7 +6700,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>744.092529296875</v>
+        <v>744.0924682617188</v>
       </c>
       <c r="C234" t="n">
         <v>753.469970703125</v>
@@ -6729,7 +6729,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>777.827392578125</v>
+        <v>777.8274536132812</v>
       </c>
       <c r="C235" t="n">
         <v>787.6300048828125</v>
@@ -6787,7 +6787,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>659.5901489257812</v>
+        <v>659.590087890625</v>
       </c>
       <c r="C237" t="n">
         <v>667</v>
@@ -6874,7 +6874,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>628.1817626953125</v>
+        <v>628.1818237304688</v>
       </c>
       <c r="C240" t="n">
         <v>634.0800170898438</v>
@@ -6903,7 +6903,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>656.2581176757812</v>
+        <v>656.2581787109375</v>
       </c>
       <c r="C241" t="n">
         <v>662.4199829101562</v>
@@ -6932,7 +6932,7 @@
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>495.1893920898438</v>
+        <v>495.1894226074219</v>
       </c>
       <c r="C242" t="n">
         <v>498.9200134277344</v>
@@ -6990,7 +6990,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>429.14697265625</v>
+        <v>429.1469421386719</v>
       </c>
       <c r="C244" t="n">
         <v>432.3800048828125</v>
